--- a/results/feature_selection/induction/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/induction/wrapper/P/metrics_global.xlsx
@@ -488,235 +488,235 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, I, FS_calc, Plag1, V_calc</t>
+          <t>t, t_ind, t_ind_ad, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9454421535528851</v>
+        <v>0.7635116982007657</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07493994129978689</v>
+        <v>0.1818699263939187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01267411810999024</v>
+        <v>0.0549376645857878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1125793858128132</v>
+        <v>0.2343878507640441</v>
       </c>
       <c r="H2" t="n">
-        <v>18.17107161906</v>
+        <v>53.18200570940681</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02773923661112765</v>
+        <v>0.1114028557498218</v>
       </c>
       <c r="J2" t="n">
-        <v>-225.8824386885151</v>
+        <v>-148.6840298140698</v>
       </c>
       <c r="K2" t="n">
-        <v>-215.9375184556937</v>
+        <v>-140.7280936278127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>tweedie</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T, I, FS_calc, Plag1, V_calc</t>
+          <t>t_ind, t_ind_ad, I</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9414217937174951</v>
+        <v>0.6664239022708821</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07372713994941023</v>
+        <v>0.1853825456117247</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01360807204542987</v>
+        <v>0.07749174750485519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1166536413723544</v>
+        <v>0.2783733958280769</v>
       </c>
       <c r="H3" t="n">
-        <v>17.20408743140707</v>
+        <v>54.34538814294506</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02959911231655237</v>
+        <v>0.155817052572134</v>
       </c>
       <c r="J3" t="n">
-        <v>-222.042974996177</v>
+        <v>-132.1095269334518</v>
       </c>
       <c r="K3" t="n">
-        <v>-212.0980547633556</v>
+        <v>-126.142574793759</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, I, FS_calc, Plag1, V_calc</t>
+          <t>t, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9407006640035369</v>
+        <v>0.5251114812537746</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07449140006035779</v>
+        <v>0.2211390976819302</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01377559484485321</v>
+        <v>0.1103194786381869</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1173694800399712</v>
+        <v>0.3321437620040258</v>
       </c>
       <c r="H4" t="n">
-        <v>17.23820470118994</v>
+        <v>60.25747828630371</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02993271719033617</v>
+        <v>0.2206901906705985</v>
       </c>
       <c r="J4" t="n">
-        <v>-221.3822640650874</v>
+        <v>-115.0362376563029</v>
       </c>
       <c r="K4" t="n">
-        <v>-211.437343832266</v>
+        <v>-111.0582695631744</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FS_calc, Plag1, V_calc</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9272452389247545</v>
+        <v>0.4582714769806139</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08431393779709347</v>
+        <v>0.239213246157823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01690137157128466</v>
+        <v>0.1258468163869644</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1300052751671434</v>
+        <v>0.3547489483944447</v>
       </c>
       <c r="H5" t="n">
-        <v>20.08801141897257</v>
+        <v>76.37849295853572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03515738842247291</v>
+        <v>0.2526113283766909</v>
       </c>
       <c r="J5" t="n">
-        <v>-214.3394671232315</v>
+        <v>-103.9252521487374</v>
       </c>
       <c r="K5" t="n">
-        <v>-208.3725149835387</v>
+        <v>-95.96931596248027</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.91135153208422</v>
+        <v>0.4572826558873836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1040890013472645</v>
+        <v>0.2388739150452779</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02059357591622259</v>
+        <v>0.1260765255148237</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1435046198427862</v>
+        <v>0.3550725637314487</v>
       </c>
       <c r="H6" t="n">
-        <v>30.48130564459194</v>
+        <v>76.14816034427578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0470100435160898</v>
+        <v>0.2530687710941616</v>
       </c>
       <c r="J6" t="n">
-        <v>-185.6699094296237</v>
+        <v>-103.826775395861</v>
       </c>
       <c r="K6" t="n">
-        <v>-161.8021008708524</v>
+        <v>-95.8708392096039</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tweedie</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, I, FS_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9075125403484724</v>
+        <v>0.4523980499727105</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1059361995883787</v>
+        <v>0.2361886202988963</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0214853969438232</v>
+        <v>0.1272112490480067</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1465789785195108</v>
+        <v>0.356666860036094</v>
       </c>
       <c r="H7" t="n">
-        <v>30.89307397909526</v>
+        <v>74.51412168534777</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04878601575613453</v>
+        <v>0.2553284593417915</v>
       </c>
       <c r="J7" t="n">
-        <v>-183.3806164727622</v>
+        <v>-103.3429345880142</v>
       </c>
       <c r="K7" t="n">
-        <v>-159.5128079139909</v>
+        <v>-95.38699840175713</v>
       </c>
     </row>
     <row r="8">
@@ -726,153 +726,153 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I, FS_calc, Plag1</t>
+          <t>t_ind_ad, I</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9004697032701888</v>
+        <v>0.1272107613222682</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09747843588065115</v>
+        <v>0.2662606601379932</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02312149064569081</v>
+        <v>0.2027542254046394</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1520575241337659</v>
+        <v>0.4502823840709732</v>
       </c>
       <c r="H8" t="n">
-        <v>24.10629287895846</v>
+        <v>66.88582917246497</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04754413247092693</v>
+        <v>0.4047647293865672</v>
       </c>
       <c r="J8" t="n">
-        <v>-197.4176091999347</v>
+        <v>-82.17108026979776</v>
       </c>
       <c r="K8" t="n">
-        <v>-191.4506570602418</v>
+        <v>-78.1931121766692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>I, Plag1</t>
+          <t>t_ind_ad, T, I, FS_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8823228345789351</v>
+        <v>0.03635547271483452</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08790032343591053</v>
+        <v>0.2245925383112635</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02733711813279071</v>
+        <v>0.2238604591311496</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1653394028439401</v>
+        <v>0.4731389427336854</v>
       </c>
       <c r="H9" t="n">
-        <v>18.35531583611893</v>
+        <v>38.49607885935198</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05543913231927297</v>
+        <v>0.4477956795773544</v>
       </c>
       <c r="J9" t="n">
-        <v>-190.3735325317465</v>
+        <v>-72.82354806362589</v>
       </c>
       <c r="K9" t="n">
-        <v>-186.395564438618</v>
+        <v>-64.8676118773688</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>I, FS_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8582066427858458</v>
+        <v>0.0250927051514378</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1219596856328071</v>
+        <v>0.2419069169946208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03293945552426146</v>
+        <v>0.226476868238907</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1814923015564612</v>
+        <v>0.4758958586065937</v>
       </c>
       <c r="H10" t="n">
-        <v>30.77209318329383</v>
+        <v>61.21518358501164</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06609562603122929</v>
+        <v>0.4520059962218036</v>
       </c>
       <c r="J10" t="n">
-        <v>-182.3065405191176</v>
+        <v>-76.19607317776496</v>
       </c>
       <c r="K10" t="n">
-        <v>-180.3175564725533</v>
+        <v>-72.21810508463641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>t_ind_ad, I</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8493168263055335</v>
+        <v>-0.008756608131367916</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1204387608351068</v>
+        <v>0.3025390773945941</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03500461372578307</v>
+        <v>0.2343402686922991</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1870951996331896</v>
+        <v>0.4840870466065985</v>
       </c>
       <c r="H11" t="n">
-        <v>31.55517747134644</v>
+        <v>71.78419377006901</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0702081817163881</v>
+        <v>0.9353303410480396</v>
       </c>
       <c r="J11" t="n">
-        <v>-179.0228718939573</v>
+        <v>-74.35297832815856</v>
       </c>
       <c r="K11" t="n">
-        <v>-177.033887847393</v>
+        <v>-70.37501023503</v>
       </c>
     </row>
     <row r="12">
@@ -882,36 +882,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, T, FS_calc, Plag1, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>dXdt_calc</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.3913323968439131</v>
+        <v>-0.225073406216284</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2514612518568239</v>
+        <v>0.2929967864090604</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1413971700588057</v>
+        <v>0.2845919708147556</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3760281506201441</v>
+        <v>0.5334716213771409</v>
       </c>
       <c r="H12" t="n">
-        <v>55.29479574792515</v>
+        <v>66.27739406169238</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2865782999879901</v>
+        <v>1.134472802870428</v>
       </c>
       <c r="J12" t="n">
-        <v>-85.63385713020989</v>
+        <v>-65.86173551861066</v>
       </c>
       <c r="K12" t="n">
-        <v>-65.74401666456714</v>
+        <v>-63.87275147204638</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wrapper/P/metrics_global.xlsx
+++ b/results/feature_selection/induction/wrapper/P/metrics_global.xlsx
@@ -496,32 +496,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>t, t_ind, t_ind_ad, V_calc</t>
+          <t>t, t_ind_ad, T, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7635116982007657</v>
+        <v>0.7198578408573513</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1818699263939187</v>
+        <v>0.189036563618508</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0549376645857878</v>
+        <v>0.06507871999682589</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2343878507640441</v>
+        <v>0.2551053115809741</v>
       </c>
       <c r="H2" t="n">
-        <v>53.18200570940681</v>
+        <v>52.73353915626484</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1114028557498218</v>
+        <v>0.1315977517405728</v>
       </c>
       <c r="J2" t="n">
-        <v>-148.6840298140698</v>
+        <v>-139.5365139086118</v>
       </c>
       <c r="K2" t="n">
-        <v>-140.7280936278127</v>
+        <v>-131.5805777223547</v>
       </c>
     </row>
     <row r="3">
@@ -531,36 +531,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>t_ind, t_ind_ad, I</t>
+          <t>t, t_ind_ad, I, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6664239022708821</v>
+        <v>0.6939671858128384</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1853825456117247</v>
+        <v>0.1931476706898532</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07749174750485519</v>
+        <v>0.07109327594703649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2783733958280769</v>
+        <v>0.2666332236369588</v>
       </c>
       <c r="H3" t="n">
-        <v>54.34538814294506</v>
+        <v>54.42678817672388</v>
       </c>
       <c r="I3" t="n">
-        <v>0.155817052572134</v>
+        <v>0.143575137419074</v>
       </c>
       <c r="J3" t="n">
-        <v>-132.1095269334518</v>
+        <v>-134.7631759945057</v>
       </c>
       <c r="K3" t="n">
-        <v>-126.142574793759</v>
+        <v>-126.8072398082486</v>
       </c>
     </row>
     <row r="4">
@@ -605,46 +605,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_b</t>
+          <t>poisson</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>t_ind_ad, T, I, V_calc</t>
+          <t>t, t_ind_ad, T, I, FS_calc, X_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4582714769806139</v>
+        <v>0.5031921038314234</v>
       </c>
       <c r="E5" t="n">
-        <v>0.239213246157823</v>
+        <v>0.1953117303647846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1258468163869644</v>
+        <v>0.115411482748313</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3547489483944447</v>
+        <v>0.3397226556300197</v>
       </c>
       <c r="H5" t="n">
-        <v>76.37849295853572</v>
+        <v>38.54149692425391</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2526113283766909</v>
+        <v>0.234330406774392</v>
       </c>
       <c r="J5" t="n">
-        <v>-103.9252521487374</v>
+        <v>-98.59957700256683</v>
       </c>
       <c r="K5" t="n">
-        <v>-95.96931596248027</v>
+        <v>-80.69872058348835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>elasticnet_b</t>
+          <t>LASSO_b</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -656,34 +656,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4572826558873836</v>
+        <v>0.4582714769806139</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2388739150452779</v>
+        <v>0.239213246157823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1260765255148237</v>
+        <v>0.1258468163869644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3550725637314487</v>
+        <v>0.3547489483944447</v>
       </c>
       <c r="H6" t="n">
-        <v>76.14816034427578</v>
+        <v>76.37849295853572</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2530687710941616</v>
+        <v>0.2526113283766909</v>
       </c>
       <c r="J6" t="n">
-        <v>-103.826775395861</v>
+        <v>-103.9252521487374</v>
       </c>
       <c r="K6" t="n">
-        <v>-95.8708392096039</v>
+        <v>-95.96931596248027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ridge_b</t>
+          <t>elasticnet_b</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -695,151 +695,151 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4523980499727105</v>
+        <v>0.4572826558873836</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2361886202988963</v>
+        <v>0.2388739150452779</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1272112490480067</v>
+        <v>0.1260765255148237</v>
       </c>
       <c r="G7" t="n">
-        <v>0.356666860036094</v>
+        <v>0.3550725637314487</v>
       </c>
       <c r="H7" t="n">
-        <v>74.51412168534777</v>
+        <v>76.14816034427578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2553284593417915</v>
+        <v>0.2530687710941616</v>
       </c>
       <c r="J7" t="n">
-        <v>-103.3429345880142</v>
+        <v>-103.826775395861</v>
       </c>
       <c r="K7" t="n">
-        <v>-95.38699840175713</v>
+        <v>-95.8708392096039</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>Ridge_b</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>t_ind_ad, I</t>
+          <t>t_ind_ad, T, I, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1272107613222682</v>
+        <v>0.4523980499727105</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2662606601379932</v>
+        <v>0.2361886202988963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2027542254046394</v>
+        <v>0.1272112490480067</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4502823840709732</v>
+        <v>0.356666860036094</v>
       </c>
       <c r="H8" t="n">
-        <v>66.88582917246497</v>
+        <v>74.51412168534777</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4047647293865672</v>
+        <v>0.2553284593417915</v>
       </c>
       <c r="J8" t="n">
-        <v>-82.17108026979776</v>
+        <v>-103.3429345880142</v>
       </c>
       <c r="K8" t="n">
-        <v>-78.1931121766692</v>
+        <v>-95.38699840175713</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_b</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>t_ind_ad, T, I, FS_calc</t>
+          <t>t_ind_ad, I</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.03635547271483452</v>
+        <v>0.1272107613222682</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2245925383112635</v>
+        <v>0.2662606601379932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2238604591311496</v>
+        <v>0.2027542254046394</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4731389427336854</v>
+        <v>0.4502823840709732</v>
       </c>
       <c r="H9" t="n">
-        <v>38.49607885935198</v>
+        <v>66.88582917246497</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4477956795773544</v>
+        <v>0.4047647293865672</v>
       </c>
       <c r="J9" t="n">
-        <v>-72.82354806362589</v>
+        <v>-82.17108026979776</v>
       </c>
       <c r="K9" t="n">
-        <v>-64.8676118773688</v>
+        <v>-78.1931121766692</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>rf_b</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I, FS_calc</t>
+          <t>t, t_ind_ad, T, I, FS_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0250927051514378</v>
+        <v>0.07798279175819367</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2419069169946208</v>
+        <v>0.2099183897022936</v>
       </c>
       <c r="F10" t="n">
-        <v>0.226476868238907</v>
+        <v>0.2141901808391134</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4758958586065937</v>
+        <v>0.4628068504669237</v>
       </c>
       <c r="H10" t="n">
-        <v>61.21518358501164</v>
+        <v>32.44379414363007</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4520059962218036</v>
+        <v>0.4290382890599214</v>
       </c>
       <c r="J10" t="n">
-        <v>-76.19607317776496</v>
+        <v>-73.20811200774897</v>
       </c>
       <c r="K10" t="n">
-        <v>-72.21810508463641</v>
+        <v>-63.26319177492759</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>poisson</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -847,32 +847,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>t_ind_ad, I</t>
+          <t>I, FS_calc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.008756608131367916</v>
+        <v>0.0250927051514378</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3025390773945941</v>
+        <v>0.2419069169946208</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2343402686922991</v>
+        <v>0.226476868238907</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4840870466065985</v>
+        <v>0.4758958586065937</v>
       </c>
       <c r="H11" t="n">
-        <v>71.78419377006901</v>
+        <v>61.21518358501164</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9353303410480396</v>
+        <v>0.4520059962218036</v>
       </c>
       <c r="J11" t="n">
-        <v>-74.35297832815856</v>
+        <v>-76.19607317776496</v>
       </c>
       <c r="K11" t="n">
-        <v>-70.37501023503</v>
+        <v>-72.21810508463641</v>
       </c>
     </row>
     <row r="12">
